--- a/grids/rts96_scenario2_droop.xlsx
+++ b/grids/rts96_scenario2_droop.xlsx
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-52605173.6</v>
+        <v>-52605210.2891637</v>
       </c>
       <c r="I2" t="n">
         <v>-50000000</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-70670121.3</v>
+        <v>-70670074.2603365</v>
       </c>
       <c r="I3" t="n">
         <v>50000000</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>150420299.6</v>
+        <v>150420308.4637028</v>
       </c>
       <c r="I4" t="n">
         <v>-130000000</v>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-128445317.2</v>
+        <v>-128445345.7458654</v>
       </c>
       <c r="I5" t="n">
         <v>-75900000</v>
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>56172467.2</v>
+        <v>56172470.68692811</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1105,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>117476012.5</v>
+        <v>117475956.01730603</v>
       </c>
       <c r="I7" t="n">
         <v>10000000</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-55706406.2</v>
+        <v>-55706431.36388873</v>
       </c>
       <c r="I8" t="n">
         <v>-20000000</v>
@@ -4362,15 +4362,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="4.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="7.33203125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="9.5" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="11.1640625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="14.83203125" bestFit="1" customWidth="1" min="2" max="4"/>
+    <col width="7.33203125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="9.5" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="11.1640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4381,25 +4381,35 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Nominal Current</t>
+          <t>Z_p</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>I_p</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P_p</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>V0 [pu]</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>V_base [V]</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>VM min [pu]</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>VM max [pu]</t>
         </is>
@@ -4413,15 +4423,21 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>150000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>0.9</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4433,15 +4449,21 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>150000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4453,15 +4475,21 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
         <v>150000</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4473,15 +4501,21 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
         <v>300000</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4493,15 +4527,21 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>300000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4513,15 +4553,21 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>300000</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4533,15 +4579,21 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>300000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>1.1</v>
       </c>
     </row>
